--- a/data/trans_dic/IP12B$vomitos-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$vomitos-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por vómitos</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,62</t>
+          <t>0,0; 38,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,42</t>
+          <t>0,0; 26,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,49</t>
+          <t>0,0; 32,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,45</t>
+          <t>0,0; 20,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,33</t>
+          <t>0,0; 19,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,44</t>
+          <t>0,0; 32,25</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,8</t>
+          <t>0,0; 52,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,01</t>
+          <t>0,0; 39,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,22</t>
+          <t>0,0; 54,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 40,33</t>
+          <t>4,62; 39,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,82</t>
+          <t>0,0; 22,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,05</t>
+          <t>0,0; 23,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,91</t>
+          <t>0,0; 19,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,45</t>
+          <t>0,0; 29,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,69</t>
+          <t>0,0; 20,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,71</t>
+          <t>0,0; 15,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,53</t>
+          <t>0,0; 11,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,08</t>
+          <t>0,0; 9,39</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,17</t>
+          <t>0,0; 39,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,59</t>
+          <t>0,0; 19,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,28</t>
+          <t>0,0; 54,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,47</t>
+          <t>0,0; 44,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,4</t>
+          <t>1,48; 13,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,11</t>
+          <t>0,0; 7,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,77</t>
+          <t>0,0; 7,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 11,25</t>
+          <t>1,36; 11,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 10,95</t>
+          <t>1,09; 10,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,57</t>
+          <t>0,0; 6,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 9,1</t>
+          <t>1,94; 9,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,37</t>
+          <t>1,08; 7,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,82</t>
+          <t>0,56; 5,36</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2543</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3275</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2848</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2534</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3382</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4244</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1848</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2283</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3737</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>519; 4460</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3487</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3284</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4012</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4458</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4627</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4530</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4743</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3514</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3219</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2719</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3456</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4111</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1414</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2284</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>4291</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>3698</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>614; 5609</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4812</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4087</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>637; 5211</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>639; 6201</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2870</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1710; 8581</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1294; 8406</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>555; 5295</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$vomitos-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$vomitos-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,89</t>
+          <t>0,0; 47,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,99</t>
+          <t>0,0; 31,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,22 +813,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,58</t>
+          <t>0,0; 32,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,11</t>
+          <t>0,0; 20,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,08</t>
+          <t>0,0; 23,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,25</t>
+          <t>0,0; 22,67</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,34</t>
+          <t>0,0; 52,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,54</t>
+          <t>0,0; 38,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,41</t>
+          <t>0,0; 58,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 39,71</t>
+          <t>4,58; 39,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,66</t>
+          <t>0,0; 29,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,75</t>
+          <t>0,0; 24,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,52</t>
+          <t>0,0; 18,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,13</t>
+          <t>0,0; 21,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,47</t>
+          <t>0,0; 21,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,55</t>
+          <t>0,0; 13,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,87</t>
+          <t>0,0; 11,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,39</t>
+          <t>0,0; 10,91</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,13</t>
+          <t>0,0; 29,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,1</t>
+          <t>0,0; 19,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,02</t>
+          <t>0,0; 53,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,19</t>
+          <t>0,0; 37,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 13,52</t>
+          <t>1,49; 13,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,93</t>
+          <t>0,0; 7,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,74</t>
+          <t>0,0; 7,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,16</t>
+          <t>1,37; 11,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,09; 10,58</t>
+          <t>1,08; 10,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,25</t>
+          <t>0,0; 7,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 9,73</t>
+          <t>2,06; 9,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 7,04</t>
+          <t>1,08; 7,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,36</t>
+          <t>0,57; 5,07</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2543</t>
+          <t>0; 3108</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3275</t>
+          <t>0; 3782</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1827,22 +1827,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2848</t>
+          <t>0; 2812</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2534</t>
+          <t>0; 2520</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3382</t>
+          <t>0; 4083</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4244</t>
+          <t>0; 2983</t>
         </is>
       </c>
     </row>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2283</t>
+          <t>0; 2286</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2985</t>
+          <t>0; 2914</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3737</t>
+          <t>0; 3998</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>519; 4460</t>
+          <t>515; 4457</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3487</t>
+          <t>0; 4486</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3284</t>
+          <t>0; 3334</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2138,17 +2138,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4012</t>
+          <t>0; 3751</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4458</t>
+          <t>0; 3298</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4627</t>
+          <t>0; 4971</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2158,17 +2158,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4530</t>
+          <t>0; 4060</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4743</t>
+          <t>0; 4752</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3514</t>
+          <t>0; 4085</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3219</t>
+          <t>0; 2451</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 2719</t>
+          <t>0; 2846</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3456</t>
+          <t>0; 3432</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4111</t>
+          <t>0; 3514</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>614; 5609</t>
+          <t>616; 5497</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4812</t>
+          <t>0; 4782</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4087</t>
+          <t>0; 3998</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>637; 5211</t>
+          <t>639; 5435</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>639; 6201</t>
+          <t>633; 5976</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2870</t>
+          <t>0; 3553</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1710; 8581</t>
+          <t>1818; 8681</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1294; 8406</t>
+          <t>1289; 8842</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>555; 5295</t>
+          <t>559; 5010</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$vomitos-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$vomitos-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8,01%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>9,37%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>6,48%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 39,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 40,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 32,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,0</t>
+          <t>0,0; 21,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,04</t>
+          <t>0,0; 18,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,67</t>
+          <t>0,0; 24,44</t>
         </is>
       </c>
     </row>
@@ -845,27 +845,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19,33%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>11,92%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>8,31%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19,33%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,4</t>
+          <t>0,0; 50,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,21</t>
+          <t>0,0; 65,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 36,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 39,69</t>
+          <t>4,56; 40,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,15</t>
+          <t>0,0; 20,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>4,73%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,49%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,11</t>
+          <t>0,0; 17,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 19,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,55</t>
+          <t>0,0; 24,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 17,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,94</t>
+          <t>0,0; 13,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,89</t>
+          <t>0,0; 12,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,91</t>
+          <t>0,0; 10,08</t>
         </is>
       </c>
     </row>
@@ -1065,22 +1065,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>6,4%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 29,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,99</t>
+          <t>0,0; 21,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 54,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,77</t>
+          <t>0,0; 43,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>5,58%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,33%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2,14%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 13,25</t>
+          <t>1,35; 11,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,88</t>
+          <t>1,1; 10,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1353,32 +1353,32 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 11,64</t>
+          <t>1,46; 13,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 10,19</t>
+          <t>0,0; 8,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,73</t>
+          <t>0,0; 7,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,06; 9,84</t>
+          <t>1,82; 9,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 7,41</t>
+          <t>1,07; 6,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,07</t>
+          <t>0,57; 4,82</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>613</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>787</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3108</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3782</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3452</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2656</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3935</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2812</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2520</t>
+          <t>0; 2703</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4083</t>
+          <t>0; 3249</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2983</t>
+          <t>0; 3217</t>
         </is>
       </c>
     </row>
@@ -1859,27 +1859,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1912,27 +1912,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>520</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>627</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1327</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2286</t>
+          <t>0; 3449</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2914</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3998</t>
+          <t>0; 2870</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2719</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>515; 4457</t>
+          <t>512; 4529</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4486</t>
+          <t>0; 3203</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2027,27 +2027,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1128</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>992</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3334</t>
+          <t>0; 2671</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4450</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3751</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3298</t>
+          <t>0; 3325</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4971</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3681</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4060</t>
+          <t>0; 3995</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4752</t>
+          <t>0; 5008</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4085</t>
+          <t>0; 3773</t>
         </is>
       </c>
     </row>
@@ -2185,22 +2185,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2238,22 +2238,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>527</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2451</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2400</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 2846</t>
+          <t>0; 3074</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3474</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3432</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3514</t>
+          <t>0; 4044</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2284</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>2313</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1414</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>1128</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2284</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>616; 5497</t>
+          <t>631; 5254</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4782</t>
+          <t>646; 6423</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3998</t>
+          <t>0; 3477</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>639; 5435</t>
+          <t>607; 5558</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>633; 5976</t>
+          <t>0; 4923</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3553</t>
+          <t>0; 4103</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1818; 8681</t>
+          <t>1606; 8024</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1289; 8842</t>
+          <t>1276; 7606</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>559; 5010</t>
+          <t>559; 4755</t>
         </is>
       </c>
     </row>
